--- a/synthetic/partner_collation/brightpath_contacts.xlsx
+++ b/synthetic/partner_collation/brightpath_contacts.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,9 +27,26 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00585858"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00585858"/>
+    </font>
+    <font>
+      <color rgb="00585858"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -38,11 +55,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEEEEE"/>
+        <fgColor rgb="002E7D32"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F2F5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,16 +72,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,74 +469,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Brightpath Learning · Primary Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Extracted from internal partner directory · last verified 2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>Doc ID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>doc_004</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Organisation</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Brightpath Learning LLP</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Contact Name</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Nurul Aisyah</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>aisyah@brightpath.edu.sg</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>+65 9876 5432</t>
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Programmes Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Preferred Hours</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Weekdays 9am - 6pm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/synthetic/partner_collation/brightpath_contacts.xlsx
+++ b/synthetic/partner_collation/brightpath_contacts.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -574,6 +574,18 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Escalation Contact</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ops@brightpath.edu.sg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:B2"/>
